--- a/backend/src/main/resources/templates/alltemple_template.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="150">
   <si>
     <t>中华人民共和国海关进口货物报关单</t>
   </si>
@@ -361,7 +361,7 @@
     <t>Terms of payment  T/T</t>
   </si>
   <si>
-    <t>From  SHANGHAI, CHINA</t>
+    <t>From  {departureCityEnglish}, CHINA</t>
   </si>
   <si>
     <t>To      {destinationRegion}</t>
@@ -416,7 +416,7 @@
     <t>{totalAmountWords}</t>
   </si>
   <si>
-    <t>TOTAL PACKED IN {totalCartons} CARTONS</t>
+    <t>TOTAL PACKED IN {totalCartons} {contonEN}</t>
   </si>
   <si>
     <t>N/M</t>
@@ -456,7 +456,7 @@
     <t>{.cartons}</t>
   </si>
   <si>
-    <t>CARTONS</t>
+    <t>{.contonEN}</t>
   </si>
   <si>
     <t>{.grossWeight}</t>
@@ -474,6 +474,9 @@
     <t>{.cbm}</t>
   </si>
   <si>
+    <t>{contonEN}</t>
+  </si>
+  <si>
     <t>KGS</t>
   </si>
   <si>
@@ -483,7 +486,7 @@
     <t>CBM</t>
   </si>
   <si>
-    <t>TOTAL PACKED IN  {totalCartons}  CARTONS</t>
+    <t>TOTAL PACKED IN  {totalCartons}  {contonEN}</t>
   </si>
 </sst>
 </file>
@@ -4032,30 +4035,30 @@
         <v>45</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F17" s="43" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H17" s="43" t="s">
         <v>47</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J17" s="43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:11">
       <c r="A18" s="45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="46"/>

--- a/backend/src/main/resources/templates/alltemple_template.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="139">
   <si>
     <t>中华人民共和国海关进口货物报关单</t>
   </si>
@@ -65,9 +65,6 @@
     <t>宁波梓熠科技有限公司</t>
   </si>
   <si>
-    <t>{exportCustoms}</t>
-  </si>
-  <si>
     <t>{exportDate}</t>
   </si>
   <si>
@@ -95,7 +92,7 @@
     <t>{consigneeCompany}</t>
   </si>
   <si>
-    <t>{transportMode}</t>
+    <t>{transportModeCn}</t>
   </si>
   <si>
     <t>生产销售单位</t>
@@ -303,33 +300,6 @@
   </si>
   <si>
     <t>申报要素</t>
-  </si>
-  <si>
-    <t>项号：{.no}</t>
-  </si>
-  <si>
-    <t>商品编码：{.hsCode}</t>
-  </si>
-  <si>
-    <t>商品名称：{.nameCh}</t>
-  </si>
-  <si>
-    <t>0:用途; {.purpose}</t>
-  </si>
-  <si>
-    <t>1:是否录制;{.isRecorded}</t>
-  </si>
-  <si>
-    <t>2:品牌; {.brand}</t>
-  </si>
-  <si>
-    <t>3:型号：{.model}</t>
-  </si>
-  <si>
-    <t>4:品牌类型;{.brandType}</t>
-  </si>
-  <si>
-    <t>5:出口享惠情况;{.exportPreference}</t>
   </si>
   <si>
     <t xml:space="preserve">Issuer: {shipperCompany}
@@ -448,9 +418,6 @@
   </si>
   <si>
     <t>MEAS.</t>
-  </si>
-  <si>
-    <t>{.unitg}</t>
   </si>
   <si>
     <t>{.cartons}</t>
@@ -503,7 +470,7 @@
     <numFmt numFmtId="178" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
     <numFmt numFmtId="179" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -569,18 +536,6 @@
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF191919"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF191919"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1386,159 +1341,159 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="28">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="32">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="33">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="34">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="35">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1730,219 +1685,210 @@
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2425,787 +2371,800 @@
   <dimension ref="A1:T32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.3796296296296" style="77" customWidth="1"/>
-    <col min="2" max="2" width="8.87962962962963" style="77" customWidth="1"/>
-    <col min="3" max="3" width="11.1296296296296" style="77" customWidth="1"/>
-    <col min="4" max="4" width="1.62962962962963" style="77" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6296296296296" style="77" customWidth="1"/>
-    <col min="6" max="6" width="13" style="77" customWidth="1"/>
-    <col min="7" max="7" width="9.75" style="77" customWidth="1"/>
-    <col min="8" max="8" width="11.6296296296296" style="77" customWidth="1"/>
-    <col min="9" max="9" width="10" style="77" customWidth="1"/>
-    <col min="10" max="10" width="4.62962962962963" style="77" customWidth="1"/>
-    <col min="11" max="11" width="10.3333333333333" style="77" customWidth="1"/>
-    <col min="12" max="12" width="6.5" style="77" customWidth="1"/>
-    <col min="13" max="13" width="8.75" style="77" customWidth="1"/>
-    <col min="14" max="14" width="3.87962962962963" style="77" customWidth="1"/>
-    <col min="15" max="15" width="6.75" style="77" customWidth="1"/>
-    <col min="16" max="16" width="6.62962962962963" style="77" customWidth="1"/>
-    <col min="17" max="17" width="11.8796296296296" style="77" customWidth="1"/>
-    <col min="18" max="19" width="9" style="77" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="77" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="77" customWidth="1"/>
+    <col min="1" max="1" width="14.3796296296296" style="74" customWidth="1"/>
+    <col min="2" max="2" width="8.87962962962963" style="74" customWidth="1"/>
+    <col min="3" max="3" width="11.1111111111111" style="74" customWidth="1"/>
+    <col min="4" max="4" width="4.44444444444444" style="74" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6296296296296" style="74" customWidth="1"/>
+    <col min="6" max="6" width="13" style="74" customWidth="1"/>
+    <col min="7" max="7" width="9.77777777777778" style="74" customWidth="1"/>
+    <col min="8" max="8" width="11.6666666666667" style="74" customWidth="1"/>
+    <col min="9" max="9" width="10" style="74" customWidth="1"/>
+    <col min="10" max="10" width="4.66666666666667" style="74" customWidth="1"/>
+    <col min="11" max="11" width="10.3333333333333" style="74" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="74" customWidth="1"/>
+    <col min="13" max="13" width="8.77777777777778" style="74" customWidth="1"/>
+    <col min="14" max="14" width="3.87962962962963" style="74" customWidth="1"/>
+    <col min="15" max="15" width="6.75" style="74" customWidth="1"/>
+    <col min="16" max="16" width="6.66666666666667" style="74" customWidth="1"/>
+    <col min="17" max="17" width="11.8796296296296" style="74" customWidth="1"/>
+    <col min="18" max="19" width="9" style="74" customWidth="1"/>
+    <col min="20" max="20" width="12.75" style="74" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="74" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customHeight="1" spans="1:20">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="77" t="s">
+      <c r="S1" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="73" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A2" s="79" t="s">
+    <row r="2" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="73" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="80"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-    </row>
-    <row r="3" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A3" s="82" t="s">
+      <c r="F2" s="77"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+    </row>
+    <row r="3" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A3" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="84" t="s">
+      <c r="B3" s="80"/>
+      <c r="C3" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="85"/>
-      <c r="E3" s="86" t="s">
+      <c r="D3" s="82"/>
+      <c r="E3" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88" t="s">
+      <c r="F3" s="84"/>
+      <c r="G3" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="82" t="s">
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="88" t="s">
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="85"/>
-    </row>
-    <row r="4" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A4" s="89" t="s">
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="82"/>
+    </row>
+    <row r="4" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A4" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="93" t="s">
+      <c r="B4" s="87"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="94"/>
-      <c r="G4" s="89" t="s">
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="89" t="s">
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
+      <c r="N4" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="89" t="s">
+      <c r="O4" s="87"/>
+      <c r="P4" s="87"/>
+      <c r="Q4" s="92"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:20">
+      <c r="A5" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="90"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="95"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:20">
-      <c r="A5" s="96" t="s">
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="97"/>
+    </row>
+    <row r="6" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A6" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="100"/>
-    </row>
-    <row r="6" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A6" s="82" t="s">
+      <c r="B6" s="80"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="86" t="s">
+      <c r="F6" s="84"/>
+      <c r="G6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="87"/>
-      <c r="G6" s="88" t="s">
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="85"/>
-      <c r="K6" s="101" t="s">
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="82"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:20">
+      <c r="A7" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="85"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:20">
-      <c r="A7" s="102" t="s">
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="103"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="99" t="s">
+      <c r="F7" s="97"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="78"/>
+      <c r="O7" s="78"/>
+      <c r="P7" s="78"/>
+      <c r="Q7" s="97"/>
+    </row>
+    <row r="8" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A8" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="100"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="100"/>
-    </row>
-    <row r="8" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A8" s="82" t="s">
+      <c r="B8" s="80"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="86" t="s">
+      <c r="F8" s="103"/>
+      <c r="G8" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="106"/>
-      <c r="G8" s="82" t="s">
+      <c r="H8" s="80"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="83"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="85"/>
-      <c r="K8" s="101" t="s">
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="80"/>
+      <c r="P8" s="80"/>
+      <c r="Q8" s="82"/>
+      <c r="T8" s="74"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:20">
+      <c r="A9" s="96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="78"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="85"/>
-      <c r="T8" s="77"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:20">
-      <c r="A9" s="99" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="81"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="107" t="s">
+      <c r="F9" s="97"/>
+      <c r="G9" s="104" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="78"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="78"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="78"/>
+      <c r="Q9" s="97"/>
+    </row>
+    <row r="10" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A10" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="100"/>
-      <c r="G9" s="107" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="100"/>
-    </row>
-    <row r="10" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A10" s="82" t="s">
+      <c r="B10" s="80"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="86" t="s">
+      <c r="F10" s="84"/>
+      <c r="G10" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="87"/>
-      <c r="G10" s="82" t="s">
+      <c r="H10" s="80"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="83"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="82" t="s">
+      <c r="L10" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="82"/>
+      <c r="N10" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="84" t="s">
+      <c r="O10" s="80"/>
+      <c r="P10" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="85"/>
-      <c r="N10" s="82" t="s">
+      <c r="Q10" s="82"/>
+      <c r="T10" s="74"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:20">
+      <c r="A11" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="O10" s="83"/>
-      <c r="P10" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="85"/>
-      <c r="T10" s="77"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:20">
-      <c r="A11" s="99" t="s">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="99" t="s">
+      <c r="F11" s="101"/>
+      <c r="G11" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="104"/>
-      <c r="G11" s="99" t="s">
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="99" t="s">
+      <c r="L11" s="78"/>
+      <c r="M11" s="97"/>
+      <c r="N11" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="81"/>
-      <c r="M11" s="100"/>
-      <c r="N11" s="99" t="s">
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="97"/>
+    </row>
+    <row r="12" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A12" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="O11" s="81"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="100"/>
-    </row>
-    <row r="12" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A12" s="82" t="s">
+      <c r="B12" s="80"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="108" t="s">
+      <c r="F12" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="108" t="s">
+      <c r="G12" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="88" t="s">
+      <c r="H12" s="82"/>
+      <c r="I12" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="85"/>
-      <c r="I12" s="82" t="s">
+      <c r="J12" s="106"/>
+      <c r="K12" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="109"/>
-      <c r="K12" s="82" t="s">
+      <c r="L12" s="80"/>
+      <c r="M12" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="L12" s="83"/>
-      <c r="M12" s="88" t="s">
+      <c r="N12" s="80"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="N12" s="83"/>
-      <c r="O12" s="85"/>
-      <c r="P12" s="88" t="s">
+      <c r="Q12" s="82"/>
+      <c r="T12" s="74"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:20">
+      <c r="A13" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="Q12" s="85"/>
-      <c r="T12" s="77"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:20">
-      <c r="A13" s="99" t="s">
+      <c r="B13" s="78"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="81"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="99" t="s">
+      <c r="F13" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="99" t="s">
+      <c r="G13" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="99" t="s">
+      <c r="H13" s="97"/>
+      <c r="I13" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="100"/>
-      <c r="I13" s="110" t="s">
+      <c r="J13" s="95"/>
+      <c r="K13" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="98"/>
-      <c r="K13" s="111" t="s">
+      <c r="L13" s="78"/>
+      <c r="M13" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="81"/>
-      <c r="M13" s="99" t="s">
+      <c r="N13" s="78"/>
+      <c r="O13" s="97"/>
+      <c r="P13" s="96" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="81"/>
-      <c r="O13" s="100"/>
-      <c r="P13" s="99" t="s">
+      <c r="Q13" s="97"/>
+    </row>
+    <row r="14" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A14" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="Q13" s="100"/>
-    </row>
-    <row r="14" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A14" s="88" t="s">
+      <c r="B14" s="80"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="82"/>
+      <c r="T14" s="74"/>
+    </row>
+    <row r="15" s="72" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A15" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="83"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="85"/>
-      <c r="T14" s="77"/>
-    </row>
-    <row r="15" s="75" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A15" s="112" t="s">
+      <c r="B15" s="78"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="81"/>
-      <c r="C15" s="81"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="113" t="s">
+      <c r="I15" s="78"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="78"/>
+      <c r="M15" s="78"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="78"/>
+      <c r="Q15" s="97"/>
+      <c r="T15" s="74"/>
+    </row>
+    <row r="16" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A16" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="100"/>
-      <c r="T15" s="77"/>
-    </row>
-    <row r="16" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A16" s="86" t="s">
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="113"/>
+      <c r="T16" s="74"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A17" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="114"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="114"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="114"/>
-      <c r="M16" s="114"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="116"/>
-      <c r="T16" s="77"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A17" s="99" t="s">
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="97"/>
+    </row>
+    <row r="18" s="73" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
+      <c r="A18" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="100"/>
-    </row>
-    <row r="18" s="76" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
-      <c r="A18" s="117" t="s">
+      <c r="B18" s="115" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="118" t="s">
+      <c r="C18" s="116"/>
+      <c r="D18" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="119"/>
-      <c r="D18" s="118" t="s">
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="119"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="118" t="s">
+      <c r="H18" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="118" t="s">
+      <c r="I18" s="116"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="119"/>
-      <c r="J18" s="119"/>
-      <c r="K18" s="118" t="s">
+      <c r="L18" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="L18" s="118" t="s">
+      <c r="M18" s="116"/>
+      <c r="N18" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="M18" s="119"/>
-      <c r="N18" s="118" t="s">
+      <c r="O18" s="116"/>
+      <c r="P18" s="116"/>
+      <c r="Q18" s="117" t="s">
         <v>64</v>
       </c>
-      <c r="O18" s="119"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="120" t="s">
+      <c r="T18" s="74"/>
+    </row>
+    <row r="19" s="74" customFormat="1" spans="1:20">
+      <c r="A19" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="T18" s="77"/>
-    </row>
-    <row r="19" s="77" customFormat="1" spans="1:20">
-      <c r="A19" s="121" t="s">
+      <c r="B19" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="122" t="s">
+      <c r="C19" s="80"/>
+      <c r="D19" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="83"/>
-      <c r="D19" s="122" t="s">
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="122" t="s">
+      <c r="H19" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="H19" s="123" t="s">
+      <c r="I19" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="I19" s="124" t="s">
+      <c r="J19" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="J19" s="125" t="s">
+      <c r="K19" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="K19" s="126" t="s">
+      <c r="L19" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="L19" s="122" t="s">
+      <c r="M19" s="80"/>
+      <c r="N19" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="M19" s="83"/>
-      <c r="N19" s="122" t="s">
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="124" t="s">
         <v>75</v>
       </c>
-      <c r="O19" s="83"/>
-      <c r="P19" s="83"/>
-      <c r="Q19" s="127" t="s">
+      <c r="R19" s="125"/>
+    </row>
+    <row r="20" s="74" customFormat="1" spans="1:20">
+      <c r="A20" s="126"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="R19" s="128"/>
-    </row>
-    <row r="20" s="77" customFormat="1" spans="1:20">
-      <c r="A20" s="129"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="131" t="s">
+      <c r="E20" s="128"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="132" t="s">
+      <c r="H20" s="130"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="127"/>
+      <c r="M20" s="127"/>
+      <c r="N20" s="127"/>
+      <c r="O20" s="127"/>
+      <c r="P20" s="127"/>
+      <c r="Q20" s="133"/>
+      <c r="R20" s="125"/>
+    </row>
+    <row r="21" s="74" customFormat="1" ht="39" customHeight="1" spans="1:20">
+      <c r="A21" s="126"/>
+      <c r="B21" s="127"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="134"/>
+      <c r="K21" s="135"/>
+      <c r="L21" s="127"/>
+      <c r="N21" s="127"/>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="125"/>
+    </row>
+    <row r="22" s="74" customFormat="1" spans="1:20">
+      <c r="A22" s="118"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="121"/>
+      <c r="J22" s="122"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="124"/>
+      <c r="R22" s="125"/>
+    </row>
+    <row r="23" s="74" customFormat="1" spans="1:20">
+      <c r="A23" s="126"/>
+      <c r="B23" s="127"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="130"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="127"/>
+      <c r="N23" s="127"/>
+      <c r="O23" s="127"/>
+      <c r="P23" s="127"/>
+      <c r="Q23" s="133"/>
+      <c r="R23" s="125"/>
+    </row>
+    <row r="24" s="74" customFormat="1" ht="40" customHeight="1" spans="1:20">
+      <c r="A24" s="126"/>
+      <c r="B24" s="127"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="134"/>
+      <c r="K24" s="135"/>
+      <c r="L24" s="127"/>
+      <c r="N24" s="127"/>
+      <c r="Q24" s="133"/>
+      <c r="R24" s="125"/>
+    </row>
+    <row r="25" s="74" customFormat="1" spans="1:20">
+      <c r="A25" s="118"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="122"/>
+      <c r="K25" s="123"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="119"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="124"/>
+      <c r="R25" s="125"/>
+    </row>
+    <row r="26" s="74" customFormat="1" spans="1:20">
+      <c r="A26" s="126"/>
+      <c r="B26" s="127"/>
+      <c r="C26" s="127"/>
+      <c r="D26" s="128"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="128"/>
+      <c r="G26" s="129"/>
+      <c r="H26" s="130"/>
+      <c r="I26" s="130"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="132"/>
+      <c r="L26" s="127"/>
+      <c r="M26" s="127"/>
+      <c r="N26" s="127"/>
+      <c r="O26" s="127"/>
+      <c r="P26" s="127"/>
+      <c r="Q26" s="133"/>
+      <c r="R26" s="125"/>
+    </row>
+    <row r="27" s="74" customFormat="1" ht="42" customHeight="1" spans="1:20">
+      <c r="A27" s="126"/>
+      <c r="B27" s="127"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="129"/>
+      <c r="H27" s="134"/>
+      <c r="K27" s="135"/>
+      <c r="L27" s="127"/>
+      <c r="N27" s="127"/>
+      <c r="Q27" s="133"/>
+      <c r="R27" s="125"/>
+    </row>
+    <row r="28" s="71" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A28" s="136"/>
+      <c r="B28" s="137"/>
+      <c r="C28" s="137"/>
+      <c r="D28" s="138" t="s">
         <v>78</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="133"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="135"/>
-      <c r="L20" s="130"/>
-      <c r="M20" s="130"/>
-      <c r="N20" s="130"/>
-      <c r="O20" s="130"/>
-      <c r="P20" s="130"/>
-      <c r="Q20" s="136"/>
-      <c r="R20" s="128"/>
-    </row>
-    <row r="21" s="77" customFormat="1" ht="39" customHeight="1" spans="1:20">
-      <c r="A21" s="129"/>
-      <c r="B21" s="130"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="137"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="130"/>
-      <c r="N21" s="130"/>
-      <c r="Q21" s="136"/>
-      <c r="R21" s="128"/>
-    </row>
-    <row r="22" s="77" customFormat="1" spans="1:20">
-      <c r="A22" s="121"/>
-      <c r="B22" s="122"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="123"/>
-      <c r="I22" s="124"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="126"/>
-      <c r="L22" s="122"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="122"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="83"/>
-      <c r="Q22" s="127"/>
-      <c r="R22" s="128"/>
-    </row>
-    <row r="23" s="77" customFormat="1" spans="1:20">
-      <c r="A23" s="129"/>
-      <c r="B23" s="130"/>
-      <c r="C23" s="130"/>
-      <c r="D23" s="131"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="135"/>
-      <c r="L23" s="130"/>
-      <c r="M23" s="130"/>
-      <c r="N23" s="130"/>
-      <c r="O23" s="130"/>
-      <c r="P23" s="130"/>
-      <c r="Q23" s="136"/>
-      <c r="R23" s="128"/>
-    </row>
-    <row r="24" s="77" customFormat="1" ht="40" customHeight="1" spans="1:20">
-      <c r="A24" s="129"/>
-      <c r="B24" s="130"/>
-      <c r="G24" s="132"/>
-      <c r="H24" s="137"/>
-      <c r="K24" s="138"/>
-      <c r="L24" s="130"/>
-      <c r="N24" s="130"/>
-      <c r="Q24" s="136"/>
-      <c r="R24" s="128"/>
-    </row>
-    <row r="25" s="77" customFormat="1" spans="1:20">
-      <c r="A25" s="121"/>
-      <c r="B25" s="122"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="122"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="122"/>
-      <c r="H25" s="124"/>
-      <c r="I25" s="124"/>
-      <c r="J25" s="125"/>
-      <c r="K25" s="126"/>
-      <c r="L25" s="122"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="122"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="127"/>
-      <c r="R25" s="128"/>
-    </row>
-    <row r="26" s="77" customFormat="1" spans="1:20">
-      <c r="A26" s="129"/>
-      <c r="B26" s="130"/>
-      <c r="C26" s="130"/>
-      <c r="D26" s="131"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="133"/>
-      <c r="I26" s="133"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="135"/>
-      <c r="L26" s="130"/>
-      <c r="M26" s="130"/>
-      <c r="N26" s="130"/>
-      <c r="O26" s="130"/>
-      <c r="P26" s="130"/>
-      <c r="Q26" s="136"/>
-      <c r="R26" s="128"/>
-    </row>
-    <row r="27" s="77" customFormat="1" ht="42" customHeight="1" spans="1:20">
-      <c r="A27" s="129"/>
-      <c r="B27" s="130"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="137"/>
-      <c r="K27" s="138"/>
-      <c r="L27" s="130"/>
-      <c r="N27" s="130"/>
-      <c r="Q27" s="136"/>
-      <c r="R27" s="128"/>
-    </row>
-    <row r="28" s="74" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A28" s="139"/>
-      <c r="B28" s="140"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="141" t="s">
+      <c r="E28" s="137"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="137" t="s">
         <v>79</v>
       </c>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="140" t="s">
+      <c r="H28" s="137"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="140"/>
-      <c r="I28" s="140"/>
-      <c r="J28" s="141" t="s">
+      <c r="K28" s="116"/>
+      <c r="L28" s="116"/>
+      <c r="M28" s="137"/>
+      <c r="N28" s="137"/>
+      <c r="O28" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="140"/>
-      <c r="N28" s="140"/>
-      <c r="O28" s="141" t="s">
+      <c r="P28" s="116"/>
+      <c r="Q28" s="139"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A29" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="P28" s="119"/>
-      <c r="Q28" s="142"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A29" s="82" t="s">
+      <c r="B29" s="80"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="106" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="83"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="109" t="s">
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="82"/>
+      <c r="M29" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="88" t="s">
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="82"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A30" s="86"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="87"/>
+      <c r="K30" s="87"/>
+      <c r="L30" s="87"/>
+      <c r="M30" s="96"/>
+      <c r="Q30" s="140"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A31" s="141" t="s">
         <v>85</v>
       </c>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="83"/>
-      <c r="Q29" s="85"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A30" s="89"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="90"/>
-      <c r="K30" s="90"/>
-      <c r="L30" s="90"/>
-      <c r="M30" s="99"/>
-      <c r="Q30" s="143"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A31" s="144" t="s">
+      <c r="B31" s="78"/>
+      <c r="C31" s="142"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="143"/>
+      <c r="J31" s="142" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="81"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="146"/>
-      <c r="I31" s="146"/>
-      <c r="J31" s="145" t="s">
+      <c r="K31" s="78"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="102"/>
+      <c r="N31" s="78"/>
+      <c r="O31" s="78"/>
+      <c r="P31" s="78"/>
+      <c r="Q31" s="97"/>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A32" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="K31" s="81"/>
-      <c r="L31" s="146"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="81"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="100"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A32" s="147" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="83"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="83"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="83"/>
-      <c r="P32" s="83"/>
-      <c r="Q32" s="83"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80"/>
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="80"/>
+      <c r="N32" s="80"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="80"/>
+      <c r="Q32" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="98">
@@ -3302,11 +3261,11 @@
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="A32:Q32"/>
     <mergeCell ref="M30:Q31"/>
+    <mergeCell ref="K6:Q7"/>
+    <mergeCell ref="K8:Q9"/>
+    <mergeCell ref="D20:F21"/>
+    <mergeCell ref="D23:F24"/>
     <mergeCell ref="D26:F27"/>
-    <mergeCell ref="D23:F24"/>
-    <mergeCell ref="K6:Q7"/>
-    <mergeCell ref="D20:F21"/>
-    <mergeCell ref="K8:Q9"/>
   </mergeCells>
   <pageMargins left="0.708333333333333" right="0.708333333333333" top="0.747916666666667" bottom="0.747916666666667" header="0.314583333333333" footer="0.314583333333333"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -3323,7 +3282,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="67.3796296296296" customWidth="1"/>
@@ -3332,110 +3291,8 @@
   <sheetData>
     <row r="1" customFormat="1" spans="1:1">
       <c r="A1" s="69" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" customFormat="1" spans="1:1">
-      <c r="A2" s="69"/>
-    </row>
-    <row r="3" customFormat="1" spans="1:1">
-      <c r="A3" s="69"/>
-    </row>
-    <row r="4" customFormat="1" spans="1:1">
-      <c r="A4" s="69" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:1">
-      <c r="A5" s="70" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:1">
-      <c r="A6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:1">
-      <c r="A7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:1">
-      <c r="A8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:1">
-      <c r="A9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:1">
-      <c r="A10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A11" s="71" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A12" s="71" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A13" s="72"/>
-    </row>
-    <row r="14" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A14" s="71"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A15" s="71"/>
-    </row>
-    <row r="17" customFormat="1" spans="1:1">
-      <c r="A17" s="69"/>
-    </row>
-    <row r="18" customFormat="1" spans="1:1">
-      <c r="A18" s="70"/>
-    </row>
-    <row r="24" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A24" s="71"/>
-    </row>
-    <row r="25" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A25" s="71"/>
-    </row>
-    <row r="26" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A26" s="72"/>
-    </row>
-    <row r="27" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A27" s="71"/>
-    </row>
-    <row r="28" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A28" s="71"/>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="69"/>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="69"/>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="70"/>
-    </row>
-    <row r="38" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A38" s="71"/>
-    </row>
-    <row r="39" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A39" s="71"/>
-    </row>
-    <row r="40" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A40" s="72"/>
-    </row>
-    <row r="41" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A41" s="71"/>
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3460,10 +3317,10 @@
   <sheetData>
     <row r="1" ht="47.45" customHeight="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3473,14 +3330,14 @@
     </row>
     <row r="2" ht="47.45" customHeight="1" spans="1:7">
       <c r="A2" s="6" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B2" s="7"/>
       <c r="G2" s="8"/>
     </row>
     <row r="3" ht="47.45" customHeight="1" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
@@ -3491,25 +3348,25 @@
     </row>
     <row r="4" ht="47.45" customHeight="1" spans="1:7">
       <c r="A4" s="14" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="17"/>
       <c r="E4" s="15" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="17"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:7">
       <c r="A5" s="18" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3519,14 +3376,14 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:7">
       <c r="A6" s="50" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B6" s="7"/>
       <c r="G6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:7">
       <c r="A7" s="51" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
@@ -3537,18 +3394,18 @@
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:7">
       <c r="A8" s="52" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="53" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="54" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G8" s="17"/>
     </row>
@@ -3556,36 +3413,36 @@
       <c r="A9" s="55"/>
       <c r="B9" s="56"/>
       <c r="C9" s="57" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="58" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:7">
       <c r="A10" s="59" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D10" s="60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" s="61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G10" s="62" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" ht="21.95" customHeight="1" spans="1:7">
@@ -3644,38 +3501,38 @@
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:7">
       <c r="A17" s="39" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B17" s="65" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="65" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="G17" s="67" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:7">
       <c r="A18" s="68" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G18" s="8"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:7">
       <c r="A19" s="68" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:7">
       <c r="A20" s="48" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G20" s="8"/>
     </row>
@@ -3774,10 +3631,10 @@
   <sheetData>
     <row r="1" ht="47.45" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3791,14 +3648,14 @@
     </row>
     <row r="2" ht="47.45" customHeight="1" spans="1:16">
       <c r="A2" s="6" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B2" s="7"/>
       <c r="K2" s="8"/>
     </row>
     <row r="3" ht="47.45" customHeight="1" spans="1:16">
       <c r="A3" s="9" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
@@ -3814,16 +3671,16 @@
     </row>
     <row r="4" ht="47.45" customHeight="1" spans="1:16">
       <c r="A4" s="14" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
       <c r="E4" s="17"/>
       <c r="F4" s="15" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -3833,10 +3690,10 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="18" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3850,14 +3707,14 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:16">
       <c r="A6" s="20" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B6" s="7"/>
       <c r="K6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:16">
       <c r="A7" s="21" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
@@ -3872,62 +3729,62 @@
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:16">
       <c r="A8" s="22" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="23" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="23" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="24" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="24" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="K8" s="17"/>
     </row>
     <row r="9" ht="21.95" customHeight="1" spans="1:16">
       <c r="A9" s="25" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -4023,42 +3880,42 @@
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:11">
       <c r="A17" s="39" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D17" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="F17" s="43" t="s">
+      <c r="G17" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="H17" s="43" t="s">
-        <v>47</v>
-      </c>
       <c r="I17" s="28" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="J17" s="43" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:11">
       <c r="A18" s="45" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="46"/>
@@ -4073,7 +3930,7 @@
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:11">
       <c r="A19" s="48" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K19" s="8"/>
     </row>

--- a/backend/src/main/resources/templates/alltemple_template.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -328,7 +328,7 @@
     <t>Transport details    BY  {transportMode}</t>
   </si>
   <si>
-    <t>Terms of payment  T/T</t>
+    <t>Terms of payment  {paymentMethod}</t>
   </si>
   <si>
     <t>From  {departureCityEnglish}, CHINA</t>
@@ -405,7 +405,7 @@
     <t>Transport details        BY  {transportMode}</t>
   </si>
   <si>
-    <t>Terms of payment T/T</t>
+    <t>Terms of payment {paymentMethod}</t>
   </si>
   <si>
     <t>PKGS</t>

--- a/backend/src/main/resources/templates/alltemple_template.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="137">
   <si>
     <t>中华人民共和国海关进口货物报关单</t>
   </si>
@@ -369,12 +369,6 @@
   </si>
   <si>
     <t xml:space="preserve">      TOTAL:</t>
-  </si>
-  <si>
-    <t>{totalQuantity}</t>
-  </si>
-  <si>
-    <t>PCS</t>
   </si>
   <si>
     <t>{currency}</t>
@@ -3503,36 +3497,32 @@
       <c r="A17" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>112</v>
-      </c>
+      <c r="B17" s="65"/>
+      <c r="C17" s="66"/>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="65" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G17" s="67" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:7">
       <c r="A18" s="68" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G18" s="8"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:7">
       <c r="A19" s="68" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:7">
       <c r="A20" s="48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G20" s="8"/>
     </row>
@@ -3631,10 +3621,10 @@
   <sheetData>
     <row r="1" ht="47.45" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3680,7 +3670,7 @@
       <c r="D4" s="16"/>
       <c r="E4" s="17"/>
       <c r="F4" s="15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -3690,10 +3680,10 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3736,19 +3726,19 @@
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K8" s="17"/>
     </row>
@@ -3763,28 +3753,28 @@
         <v>108</v>
       </c>
       <c r="D9" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="G9" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="H9" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="I9" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="K9" s="30" t="s">
         <v>131</v>
-      </c>
-      <c r="I9" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -3882,40 +3872,36 @@
       <c r="A17" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>112</v>
-      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="42" t="s">
         <v>44</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F17" s="43" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H17" s="43" t="s">
         <v>46</v>
       </c>
       <c r="I17" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="K17" s="44" t="s">
         <v>135</v>
-      </c>
-      <c r="J17" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="K17" s="44" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:11">
       <c r="A18" s="45" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="46"/>
@@ -3930,7 +3916,7 @@
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:11">
       <c r="A19" s="48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K19" s="8"/>
     </row>

--- a/backend/src/main/resources/templates/alltemple_template.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template.xlsx
@@ -4,16 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
-    <sheet name="申报要素" sheetId="2" r:id="rId2"/>
-    <sheet name="发票" sheetId="3" r:id="rId3"/>
-    <sheet name="装箱单" sheetId="4" r:id="rId4"/>
+    <sheet name="发票" sheetId="3" r:id="rId2"/>
+    <sheet name="装箱单" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报关单!$A$1:$R$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报关单!$E$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="136">
   <si>
     <t>中华人民共和国海关进口货物报关单</t>
   </si>
@@ -297,9 +296,6 @@
   </si>
   <si>
     <t>报关单、备案清单版式由竖版改为横版，纸质单证全部采用普通打印方式，取消套打，不在印制空白格式单证.</t>
-  </si>
-  <si>
-    <t>申报要素</t>
   </si>
   <si>
     <t xml:space="preserve">Issuer: {shipperCompany}
@@ -322,7 +318,7 @@
     <t>No:  {invoiceNo}</t>
   </si>
   <si>
-    <t>Date:  {invoiceDate}</t>
+    <t>Date:  {date}</t>
   </si>
   <si>
     <t>Transport details    BY  {transportMode}</t>
@@ -393,7 +389,7 @@
 PACKING LIST</t>
   </si>
   <si>
-    <t>Date:   {invoiceDate}</t>
+    <t>Date:   {date}</t>
   </si>
   <si>
     <t>Transport details        BY  {transportMode}</t>
@@ -464,7 +460,7 @@
     <numFmt numFmtId="178" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
     <numFmt numFmtId="179" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -524,12 +520,6 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1335,159 +1325,159 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="29">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="29">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="32">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="33">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="34">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="35">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1676,213 +1666,210 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2361,804 +2348,806 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:T32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.3796296296296" style="74" customWidth="1"/>
-    <col min="2" max="2" width="8.87962962962963" style="74" customWidth="1"/>
-    <col min="3" max="3" width="11.1111111111111" style="74" customWidth="1"/>
-    <col min="4" max="4" width="4.44444444444444" style="74" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6296296296296" style="74" customWidth="1"/>
-    <col min="6" max="6" width="13" style="74" customWidth="1"/>
-    <col min="7" max="7" width="9.77777777777778" style="74" customWidth="1"/>
-    <col min="8" max="8" width="11.6666666666667" style="74" customWidth="1"/>
-    <col min="9" max="9" width="10" style="74" customWidth="1"/>
-    <col min="10" max="10" width="4.66666666666667" style="74" customWidth="1"/>
-    <col min="11" max="11" width="10.3333333333333" style="74" customWidth="1"/>
-    <col min="12" max="12" width="6.5" style="74" customWidth="1"/>
-    <col min="13" max="13" width="8.77777777777778" style="74" customWidth="1"/>
-    <col min="14" max="14" width="3.87962962962963" style="74" customWidth="1"/>
-    <col min="15" max="15" width="6.75" style="74" customWidth="1"/>
-    <col min="16" max="16" width="6.66666666666667" style="74" customWidth="1"/>
-    <col min="17" max="17" width="11.8796296296296" style="74" customWidth="1"/>
-    <col min="18" max="19" width="9" style="74" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="74" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="74" customWidth="1"/>
+    <col min="1" max="1" width="14.3796296296296" style="73" customWidth="1"/>
+    <col min="2" max="2" width="8.87962962962963" style="73" customWidth="1"/>
+    <col min="3" max="3" width="11.1111111111111" style="73" customWidth="1"/>
+    <col min="4" max="4" width="4.44444444444444" style="73" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6296296296296" style="73" customWidth="1"/>
+    <col min="6" max="6" width="13" style="73" customWidth="1"/>
+    <col min="7" max="7" width="9.77777777777778" style="73" customWidth="1"/>
+    <col min="8" max="8" width="11.6296296296296" style="73" customWidth="1"/>
+    <col min="9" max="9" width="10" style="73" customWidth="1"/>
+    <col min="10" max="10" width="4.62962962962963" style="73" customWidth="1"/>
+    <col min="11" max="11" width="16.3333333333333" style="73" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="73" customWidth="1"/>
+    <col min="13" max="13" width="8.77777777777778" style="73" customWidth="1"/>
+    <col min="14" max="14" width="3.87962962962963" style="73" customWidth="1"/>
+    <col min="15" max="15" width="6.75" style="73" customWidth="1"/>
+    <col min="16" max="16" width="6.66666666666667" style="73" customWidth="1"/>
+    <col min="17" max="17" width="18.6666666666667" style="73" customWidth="1"/>
+    <col min="18" max="19" width="9" style="73" customWidth="1"/>
+    <col min="20" max="20" width="12.75" style="73" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="73" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customHeight="1" spans="1:20">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="74" t="s">
+      <c r="S1" s="73" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A2" s="76" t="s">
+    <row r="2" s="69" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A2" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="70" t="s">
+      <c r="C2" s="76"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-    </row>
-    <row r="3" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A3" s="79" t="s">
+      <c r="F2" s="76"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+    </row>
+    <row r="3" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A3" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81" t="s">
+      <c r="B3" s="79"/>
+      <c r="C3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83" t="s">
+      <c r="D3" s="81"/>
+      <c r="E3" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="84"/>
-      <c r="G3" s="85" t="s">
+      <c r="F3" s="83"/>
+      <c r="G3" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="79" t="s">
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="85" t="s">
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="82"/>
-    </row>
-    <row r="4" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A4" s="86" t="s">
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="81"/>
+    </row>
+    <row r="4" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A4" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="86" t="s">
+      <c r="B4" s="86"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="86" t="s">
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
-      <c r="N4" s="86" t="s">
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
+      <c r="N4" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="87"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="92"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="91"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:20">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="97"/>
-    </row>
-    <row r="6" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A6" s="79" t="s">
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="96"/>
+    </row>
+    <row r="6" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A6" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="83" t="s">
+      <c r="B6" s="79"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="84"/>
-      <c r="G6" s="85" t="s">
+      <c r="F6" s="83"/>
+      <c r="G6" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="98" t="s">
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="82"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="79"/>
+      <c r="Q6" s="81"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:20">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="96" t="s">
+      <c r="B7" s="99"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="97"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="78"/>
-      <c r="N7" s="78"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="97"/>
-    </row>
-    <row r="8" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A8" s="79" t="s">
+      <c r="F7" s="96"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="96"/>
+    </row>
+    <row r="8" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A8" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="83" t="s">
+      <c r="B8" s="79"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="103"/>
-      <c r="G8" s="79" t="s">
+      <c r="F8" s="102"/>
+      <c r="G8" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="80"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="98" t="s">
+      <c r="H8" s="79"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="80"/>
-      <c r="P8" s="80"/>
-      <c r="Q8" s="82"/>
-      <c r="T8" s="74"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
+      <c r="O8" s="79"/>
+      <c r="P8" s="79"/>
+      <c r="Q8" s="81"/>
+      <c r="T8" s="73"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:20">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="104" t="s">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="97"/>
-      <c r="G9" s="104" t="s">
+      <c r="F9" s="96"/>
+      <c r="G9" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="97"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="78"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="78"/>
-      <c r="Q9" s="97"/>
-    </row>
-    <row r="10" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A10" s="79" t="s">
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="101"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="96"/>
+    </row>
+    <row r="10" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A10" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="83" t="s">
+      <c r="B10" s="79"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="84"/>
-      <c r="G10" s="79" t="s">
+      <c r="F10" s="83"/>
+      <c r="G10" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="80"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="79" t="s">
+      <c r="H10" s="79"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="81" t="s">
+      <c r="L10" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="82"/>
-      <c r="N10" s="79" t="s">
+      <c r="M10" s="81"/>
+      <c r="N10" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="80"/>
-      <c r="P10" s="81" t="s">
+      <c r="O10" s="79"/>
+      <c r="P10" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="Q10" s="82"/>
-      <c r="T10" s="74"/>
+      <c r="Q10" s="81"/>
+      <c r="T10" s="73"/>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:20">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="96" t="s">
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="101"/>
-      <c r="G11" s="96" t="s">
+      <c r="F11" s="100"/>
+      <c r="G11" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="96" t="s">
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="L11" s="78"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="96" t="s">
+      <c r="L11" s="77"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="78"/>
-      <c r="P11" s="78"/>
-      <c r="Q11" s="97"/>
-    </row>
-    <row r="12" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A12" s="79" t="s">
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="96"/>
+    </row>
+    <row r="12" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A12" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="80"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="105" t="s">
+      <c r="B12" s="79"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="105" t="s">
+      <c r="F12" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="85" t="s">
+      <c r="G12" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="82"/>
-      <c r="I12" s="79" t="s">
+      <c r="H12" s="81"/>
+      <c r="I12" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="106"/>
-      <c r="K12" s="79" t="s">
+      <c r="J12" s="105"/>
+      <c r="K12" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="80"/>
-      <c r="M12" s="85" t="s">
+      <c r="L12" s="79"/>
+      <c r="M12" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="N12" s="80"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="85" t="s">
+      <c r="N12" s="79"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="Q12" s="82"/>
-      <c r="T12" s="74"/>
+      <c r="Q12" s="81"/>
+      <c r="T12" s="73"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:20">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="96" t="s">
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="96" t="s">
+      <c r="F13" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="96" t="s">
+      <c r="G13" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="97"/>
-      <c r="I13" s="107" t="s">
+      <c r="H13" s="96"/>
+      <c r="I13" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="95"/>
-      <c r="K13" s="108" t="s">
+      <c r="J13" s="94"/>
+      <c r="K13" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="78"/>
-      <c r="M13" s="96" t="s">
+      <c r="L13" s="77"/>
+      <c r="M13" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="78"/>
-      <c r="O13" s="97"/>
-      <c r="P13" s="96" t="s">
+      <c r="N13" s="77"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="97"/>
-    </row>
-    <row r="14" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A14" s="85" t="s">
+      <c r="Q13" s="96"/>
+    </row>
+    <row r="14" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A14" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="80"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
-      <c r="N14" s="80"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="80"/>
-      <c r="Q14" s="82"/>
-      <c r="T14" s="74"/>
-    </row>
-    <row r="15" s="72" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A15" s="109" t="s">
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="79"/>
+      <c r="P14" s="79"/>
+      <c r="Q14" s="81"/>
+      <c r="T14" s="73"/>
+    </row>
+    <row r="15" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A15" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="110" t="s">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="97"/>
-      <c r="T15" s="74"/>
-    </row>
-    <row r="16" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A16" s="83" t="s">
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="77"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="96"/>
+      <c r="T15" s="73"/>
+    </row>
+    <row r="16" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A16" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="112"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="113"/>
-      <c r="T16" s="74"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="112"/>
+      <c r="T16" s="73"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="97"/>
-    </row>
-    <row r="18" s="73" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
-      <c r="A18" s="114" t="s">
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="96"/>
+    </row>
+    <row r="18" s="72" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
+      <c r="A18" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="115" t="s">
+      <c r="B18" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="116"/>
-      <c r="D18" s="115" t="s">
+      <c r="C18" s="115"/>
+      <c r="D18" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="115" t="s">
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="114" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="115" t="s">
+      <c r="H18" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="115" t="s">
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="115" t="s">
+      <c r="L18" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="M18" s="116"/>
-      <c r="N18" s="115" t="s">
+      <c r="M18" s="115"/>
+      <c r="N18" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="O18" s="116"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="117" t="s">
+      <c r="O18" s="115"/>
+      <c r="P18" s="115"/>
+      <c r="Q18" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="T18" s="74"/>
-    </row>
-    <row r="19" s="74" customFormat="1" spans="1:20">
-      <c r="A19" s="118" t="s">
+      <c r="T18" s="73"/>
+    </row>
+    <row r="19" s="73" customFormat="1" spans="1:20">
+      <c r="A19" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="80"/>
-      <c r="D19" s="119" t="s">
+      <c r="C19" s="79"/>
+      <c r="D19" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="119" t="s">
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="120" t="s">
+      <c r="H19" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="121" t="s">
+      <c r="I19" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="122" t="s">
+      <c r="J19" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="123" t="s">
+      <c r="K19" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="119" t="s">
+      <c r="L19" s="118" t="s">
         <v>73</v>
       </c>
-      <c r="M19" s="80"/>
-      <c r="N19" s="119" t="s">
+      <c r="M19" s="79"/>
+      <c r="N19" s="118" t="s">
         <v>74</v>
       </c>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="124" t="s">
+      <c r="O19" s="79"/>
+      <c r="P19" s="79"/>
+      <c r="Q19" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="R19" s="125"/>
-    </row>
-    <row r="20" s="74" customFormat="1" spans="1:20">
-      <c r="A20" s="126"/>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="128" t="s">
+      <c r="R19" s="124"/>
+    </row>
+    <row r="20" s="73" customFormat="1" spans="1:20">
+      <c r="A20" s="125"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="127" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="129" t="s">
+      <c r="E20" s="127"/>
+      <c r="F20" s="127"/>
+      <c r="G20" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="132"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="127"/>
-      <c r="N20" s="127"/>
-      <c r="O20" s="127"/>
-      <c r="P20" s="127"/>
-      <c r="Q20" s="133"/>
-      <c r="R20" s="125"/>
-    </row>
-    <row r="21" s="74" customFormat="1" ht="39" customHeight="1" spans="1:20">
-      <c r="A21" s="126"/>
-      <c r="B21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="134"/>
-      <c r="K21" s="135"/>
-      <c r="L21" s="127"/>
-      <c r="N21" s="127"/>
-      <c r="Q21" s="133"/>
-      <c r="R21" s="125"/>
-    </row>
-    <row r="22" s="74" customFormat="1" spans="1:20">
-      <c r="A22" s="118"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="121"/>
-      <c r="J22" s="122"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="119"/>
-      <c r="M22" s="80"/>
-      <c r="N22" s="119"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="124"/>
-      <c r="R22" s="125"/>
-    </row>
-    <row r="23" s="74" customFormat="1" spans="1:20">
-      <c r="A23" s="126"/>
-      <c r="B23" s="127"/>
-      <c r="C23" s="127"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="130"/>
-      <c r="I23" s="130"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="132"/>
-      <c r="L23" s="127"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="127"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="127"/>
-      <c r="Q23" s="133"/>
-      <c r="R23" s="125"/>
-    </row>
-    <row r="24" s="74" customFormat="1" ht="40" customHeight="1" spans="1:20">
-      <c r="A24" s="126"/>
-      <c r="B24" s="127"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="134"/>
-      <c r="K24" s="135"/>
-      <c r="L24" s="127"/>
-      <c r="N24" s="127"/>
-      <c r="Q24" s="133"/>
-      <c r="R24" s="125"/>
-    </row>
-    <row r="25" s="74" customFormat="1" spans="1:20">
-      <c r="A25" s="118"/>
-      <c r="B25" s="119"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="122"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="119"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="124"/>
-      <c r="R25" s="125"/>
-    </row>
-    <row r="26" s="74" customFormat="1" spans="1:20">
-      <c r="A26" s="126"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="127"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="128"/>
-      <c r="F26" s="128"/>
-      <c r="G26" s="129"/>
-      <c r="H26" s="130"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="131"/>
-      <c r="K26" s="132"/>
-      <c r="L26" s="127"/>
-      <c r="M26" s="127"/>
-      <c r="N26" s="127"/>
-      <c r="O26" s="127"/>
-      <c r="P26" s="127"/>
-      <c r="Q26" s="133"/>
-      <c r="R26" s="125"/>
-    </row>
-    <row r="27" s="74" customFormat="1" ht="42" customHeight="1" spans="1:20">
-      <c r="A27" s="126"/>
-      <c r="B27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="128"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="134"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="127"/>
-      <c r="N27" s="127"/>
-      <c r="Q27" s="133"/>
-      <c r="R27" s="125"/>
-    </row>
-    <row r="28" s="71" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A28" s="136"/>
-      <c r="B28" s="137"/>
-      <c r="C28" s="137"/>
-      <c r="D28" s="138" t="s">
+      <c r="H20" s="129"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="130"/>
+      <c r="K20" s="131"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="126"/>
+      <c r="O20" s="126"/>
+      <c r="P20" s="126"/>
+      <c r="Q20" s="132"/>
+      <c r="R20" s="124"/>
+    </row>
+    <row r="21" s="73" customFormat="1" ht="39" customHeight="1" spans="1:20">
+      <c r="A21" s="125"/>
+      <c r="B21" s="126"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="127"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="133"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="Q21" s="132"/>
+      <c r="R21" s="124"/>
+    </row>
+    <row r="22" s="73" customFormat="1" spans="1:20">
+      <c r="A22" s="117"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="120"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="79"/>
+      <c r="Q22" s="123"/>
+      <c r="R22" s="124"/>
+    </row>
+    <row r="23" s="73" customFormat="1" spans="1:20">
+      <c r="A23" s="125"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="126"/>
+      <c r="N23" s="126"/>
+      <c r="O23" s="126"/>
+      <c r="P23" s="126"/>
+      <c r="Q23" s="132"/>
+      <c r="R23" s="124"/>
+    </row>
+    <row r="24" s="73" customFormat="1" ht="40" customHeight="1" spans="1:20">
+      <c r="A24" s="125"/>
+      <c r="B24" s="126"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="133"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="126"/>
+      <c r="N24" s="126"/>
+      <c r="Q24" s="132"/>
+      <c r="R24" s="124"/>
+    </row>
+    <row r="25" s="73" customFormat="1" spans="1:20">
+      <c r="A25" s="117"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="120"/>
+      <c r="I25" s="120"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="118"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="118"/>
+      <c r="O25" s="79"/>
+      <c r="P25" s="79"/>
+      <c r="Q25" s="123"/>
+      <c r="R25" s="124"/>
+    </row>
+    <row r="26" s="73" customFormat="1" spans="1:20">
+      <c r="A26" s="125"/>
+      <c r="B26" s="126"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="127"/>
+      <c r="E26" s="127"/>
+      <c r="F26" s="127"/>
+      <c r="G26" s="128"/>
+      <c r="H26" s="129"/>
+      <c r="I26" s="129"/>
+      <c r="J26" s="130"/>
+      <c r="K26" s="131"/>
+      <c r="L26" s="126"/>
+      <c r="M26" s="126"/>
+      <c r="N26" s="126"/>
+      <c r="O26" s="126"/>
+      <c r="P26" s="126"/>
+      <c r="Q26" s="132"/>
+      <c r="R26" s="124"/>
+    </row>
+    <row r="27" s="73" customFormat="1" ht="42" customHeight="1" spans="1:20">
+      <c r="A27" s="125"/>
+      <c r="B27" s="126"/>
+      <c r="D27" s="127"/>
+      <c r="E27" s="127"/>
+      <c r="F27" s="127"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="133"/>
+      <c r="K27" s="134"/>
+      <c r="L27" s="126"/>
+      <c r="N27" s="126"/>
+      <c r="Q27" s="132"/>
+      <c r="R27" s="124"/>
+    </row>
+    <row r="28" s="70" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A28" s="135"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="137" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137" t="s">
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="137"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="138" t="s">
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="137" t="s">
         <v>80</v>
       </c>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="137"/>
-      <c r="O28" s="138" t="s">
+      <c r="K28" s="115"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="136"/>
+      <c r="O28" s="137" t="s">
         <v>81</v>
       </c>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="139"/>
+      <c r="P28" s="115"/>
+      <c r="Q28" s="138"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="106" t="s">
+      <c r="B29" s="79"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="80"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="85" t="s">
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="N29" s="80"/>
-      <c r="O29" s="80"/>
-      <c r="P29" s="80"/>
-      <c r="Q29" s="82"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="81"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A30" s="86"/>
-      <c r="B30" s="87"/>
-      <c r="C30" s="87"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="87"/>
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="96"/>
-      <c r="Q30" s="140"/>
+      <c r="A30" s="85"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="86"/>
+      <c r="L30" s="86"/>
+      <c r="M30" s="95"/>
+      <c r="Q30" s="139"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A31" s="141" t="s">
+      <c r="A31" s="140" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="78"/>
-      <c r="C31" s="142"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="143"/>
-      <c r="I31" s="143"/>
-      <c r="J31" s="142" t="s">
+      <c r="B31" s="77"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="142"/>
+      <c r="I31" s="142"/>
+      <c r="J31" s="141" t="s">
         <v>86</v>
       </c>
-      <c r="K31" s="78"/>
-      <c r="L31" s="143"/>
-      <c r="M31" s="102"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="97"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="142"/>
+      <c r="M31" s="101"/>
+      <c r="N31" s="77"/>
+      <c r="O31" s="77"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="96"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A32" s="144" t="s">
+      <c r="A32" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="80"/>
-      <c r="N32" s="80"/>
-      <c r="O32" s="80"/>
-      <c r="P32" s="80"/>
-      <c r="Q32" s="80"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="79"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="79"/>
+      <c r="O32" s="79"/>
+      <c r="P32" s="79"/>
+      <c r="Q32" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="98">
@@ -3276,28 +3265,6 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="67.3796296296296" customWidth="1"/>
-    <col min="2" max="16384" width="9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="1" spans="1:1">
-      <c r="A1" s="69" t="s">
-        <v>88</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="89" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
@@ -3311,10 +3278,10 @@
   <sheetData>
     <row r="1" ht="47.45" customHeight="1" spans="1:7">
       <c r="A1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="49" t="s">
         <v>89</v>
-      </c>
-      <c r="B1" s="49" t="s">
-        <v>90</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3324,14 +3291,14 @@
     </row>
     <row r="2" ht="47.45" customHeight="1" spans="1:7">
       <c r="A2" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="7"/>
       <c r="G2" s="8"/>
     </row>
     <row r="3" ht="47.45" customHeight="1" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
@@ -3342,25 +3309,25 @@
     </row>
     <row r="4" ht="47.45" customHeight="1" spans="1:7">
       <c r="A4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>93</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>94</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="17"/>
       <c r="E4" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="17"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:7">
       <c r="A5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>96</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>97</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3370,14 +3337,14 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:7">
       <c r="A6" s="50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" s="7"/>
       <c r="G6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:7">
       <c r="A7" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
@@ -3388,18 +3355,18 @@
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:7">
       <c r="A8" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>100</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>101</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G8" s="17"/>
     </row>
@@ -3407,24 +3374,24 @@
       <c r="A9" s="55"/>
       <c r="B9" s="56"/>
       <c r="C9" s="57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="58" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:7">
       <c r="A10" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="C10" s="61" t="s">
         <v>107</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>108</v>
       </c>
       <c r="D10" s="60" t="s">
         <v>71</v>
@@ -3436,7 +3403,7 @@
         <v>71</v>
       </c>
       <c r="G10" s="62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="21.95" customHeight="1" spans="1:7">
@@ -3495,34 +3462,34 @@
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:7">
       <c r="A17" s="39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B17" s="65"/>
       <c r="C17" s="66"/>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="67" t="s">
         <v>111</v>
-      </c>
-      <c r="G17" s="67" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:7">
       <c r="A18" s="68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G18" s="8"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:7">
       <c r="A19" s="68" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:7">
       <c r="A20" s="48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G20" s="8"/>
     </row>
@@ -3595,14 +3562,17 @@
     <mergeCell ref="A20:G32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="256" scale="97" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -3621,10 +3591,10 @@
   <sheetData>
     <row r="1" ht="47.45" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3638,14 +3608,14 @@
     </row>
     <row r="2" ht="47.45" customHeight="1" spans="1:16">
       <c r="A2" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="7"/>
       <c r="K2" s="8"/>
     </row>
     <row r="3" ht="47.45" customHeight="1" spans="1:16">
       <c r="A3" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
@@ -3661,16 +3631,16 @@
     </row>
     <row r="4" ht="47.45" customHeight="1" spans="1:16">
       <c r="A4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>93</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>94</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
       <c r="E4" s="17"/>
       <c r="F4" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -3680,10 +3650,10 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>119</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>120</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3697,14 +3667,14 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:16">
       <c r="A6" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" s="7"/>
       <c r="K6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:16">
       <c r="A7" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
@@ -3719,62 +3689,62 @@
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:16">
       <c r="A8" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>101</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K8" s="17"/>
     </row>
     <row r="9" ht="21.95" customHeight="1" spans="1:16">
       <c r="A9" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="C9" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="27" t="s">
-        <v>108</v>
-      </c>
       <c r="D9" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="F9" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="G9" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="H9" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="I9" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="I9" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="J9" s="29" t="s">
+      <c r="K9" s="30" t="s">
         <v>130</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -3870,7 +3840,7 @@
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:11">
       <c r="A17" s="39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B17" s="40"/>
       <c r="C17" s="41"/>
@@ -3878,30 +3848,30 @@
         <v>44</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F17" s="43" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H17" s="43" t="s">
         <v>46</v>
       </c>
       <c r="I17" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="J17" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="J17" s="43" t="s">
+      <c r="K17" s="44" t="s">
         <v>134</v>
-      </c>
-      <c r="K17" s="44" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:11">
       <c r="A18" s="45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="46"/>
@@ -3916,7 +3886,7 @@
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:11">
       <c r="A19" s="48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K19" s="8"/>
     </row>
@@ -3996,6 +3966,7 @@
     <mergeCell ref="B1:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="256" scale="86" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/backend/src/main/resources/templates/alltemple_template.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -3150,7 +3150,7 @@
       <c r="Q32" s="79"/>
     </row>
   </sheetData>
-  <mergeCells count="98">
+  <mergeCells count="99">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -3161,6 +3161,7 @@
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="K5:M5"/>
